--- a/Result/profitability/5269.xlsx
+++ b/Result/profitability/5269.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM64"/>
+  <dimension ref="A1:AM65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.48</v>
       </c>
       <c r="M2" t="n">
-        <v>15.50625</v>
+        <v>17.27625</v>
       </c>
       <c r="N2" t="n">
-        <v>51.56874999999999</v>
+        <v>51.25</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.7</v>
       </c>
       <c r="M3" t="n">
-        <v>13.96125</v>
+        <v>15.745</v>
       </c>
       <c r="N3" t="n">
-        <v>50.4525</v>
+        <v>50.14375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -8558,6 +8558,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2723</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1353</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1370</v>
+      </c>
+      <c r="F65" t="n">
+        <v>50.32</v>
+      </c>
+      <c r="G65" t="n">
+        <v>649</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>23.83%</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>1536</v>
+      </c>
+      <c r="J65" t="n">
+        <v>2185</v>
+      </c>
+      <c r="K65" t="n">
+        <v>2017</v>
+      </c>
+      <c r="L65" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="M65" t="n">
+        <v>18.84875</v>
+      </c>
+      <c r="N65" t="n">
+        <v>52.0925</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
+      </c>
+      <c r="V65" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W65" t="n">
+        <v>2.369999999999997</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0.09537223340040235</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>-0.509999999999998</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>-0.01003344481605351</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0.8122503328894806</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>-2.170000000000002</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>-0.0413412078491141</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK65" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
